--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 17820-2024 artfynd.xlsx
+++ b/artfynd/A 17820-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537298</v>
       </c>
       <c r="B2" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136541473</v>
       </c>
       <c r="B3" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
